--- a/docs/assets/run-20260902-074613-full-stats.xlsx
+++ b/docs/assets/run-20260902-074613-full-stats.xlsx
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -587,6 +587,8 @@
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -599,7 +601,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Run ID 20260902-074613  |  Host: Pi5Backup  |  8/8 devices, all VERIFY clean  |  Transfer figures from engine.log, CPU/memory/network peaks from each device's own monitor log</t>
+          <t>Run ID 20260902-074613  |  Host: Pi5Backup  |  8/8 devices, all VERIFY clean  |  Transfer figures from engine.log, CPU/memory/network peaks from each device's own monitor log, Board Model/Architecture supplied by user</t>
         </is>
       </c>
     </row>
@@ -677,6 +679,16 @@
       <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Peak Network (B/s)</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Board Model</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Architecture</t>
         </is>
       </c>
     </row>
@@ -736,6 +748,16 @@
       <c r="O5" s="7" t="n">
         <v>7566662</v>
       </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>BeagleBone Black (K16a-b)</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>32-bit</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -793,6 +815,16 @@
       <c r="O6" s="7" t="n">
         <v>10148029.8</v>
       </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>Raspberry Pi 4B</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>64-bit</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -850,6 +882,16 @@
       <c r="O7" s="7" t="n">
         <v>13728470.7</v>
       </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>Raspberry Pi 4B</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>64-bit</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -907,6 +949,16 @@
       <c r="O8" s="7" t="n">
         <v>349327</v>
       </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>Raspberry Pi 3B</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>32-bit</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -964,6 +1016,16 @@
       <c r="O9" s="15" t="n">
         <v>27829539.6</v>
       </c>
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t>Raspberry Pi 5B</t>
+        </is>
+      </c>
+      <c r="Q9" s="12" t="inlineStr">
+        <is>
+          <t>64-bit</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1021,6 +1083,16 @@
       <c r="O10" s="7" t="n">
         <v>17921649.8</v>
       </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>Raspberry Pi 4B</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>64-bit</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1078,6 +1150,16 @@
       <c r="O11" s="7" t="n">
         <v>34350091</v>
       </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>Raspberry Pi 4B</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>32-bit</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1134,6 +1216,16 @@
       </c>
       <c r="O12" s="7" t="n">
         <v>12104032.2</v>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>Raspberry Pi 4B</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>64-bit</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1165,6 +1257,8 @@
       <c r="M13" s="21" t="n"/>
       <c r="N13" s="21" t="n"/>
       <c r="O13" s="21" t="n"/>
+      <c r="P13" s="21" t="n"/>
+      <c r="Q13" s="21" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -1312,9 +1406,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A14:O14"/>
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A14:Q14"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
